--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553748073</v>
+        <v>46157.93108265242</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108265242</v>
+        <v>46157.93132874691</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93132874691</v>
+        <v>46157.93380770802</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93380770802</v>
+        <v>46157.93691681675</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93691681675</v>
+        <v>46158.28203483719</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203483719</v>
+        <v>46158.29735310796</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29735310796</v>
+        <v>46158.29804183059</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804183059</v>
+        <v>46158.33367691436</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33367691436</v>
+        <v>46158.37219437637</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/11. ООО ЛИКАРД (топливо Лукойл)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37219437637</v>
+        <v>46158.37274060042</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
